--- a/data/gcurve_2026-07-31.xlsx
+++ b/data/gcurve_2026-07-31.xlsx
@@ -433,7 +433,7 @@
         <v>0.0028</v>
       </c>
       <c r="B2" t="n">
-        <v>13.827312</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="3">
@@ -441,7 +441,7 @@
         <v>0.0417</v>
       </c>
       <c r="B3" t="n">
-        <v>13.789968</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="4">
@@ -449,7 +449,7 @@
         <v>0.1667</v>
       </c>
       <c r="B4" t="n">
-        <v>13.669968</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="5">
@@ -577,7 +577,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="n">
-        <v>16.06</v>
+        <v>16.025</v>
       </c>
     </row>
   </sheetData>

--- a/data/gcurve_2026-07-31.xlsx
+++ b/data/gcurve_2026-07-31.xlsx
@@ -1,34 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="30">
+  <si>
+    <t>тенор</t>
+  </si>
+  <si>
+    <t>тенор_лет</t>
+  </si>
+  <si>
+    <t>T_середина_интервала</t>
+  </si>
+  <si>
+    <t>ставка</t>
+  </si>
+  <si>
+    <t>метод</t>
+  </si>
+  <si>
+    <t>интерполировано</t>
+  </si>
+  <si>
+    <t>экстраполировано</t>
+  </si>
+  <si>
+    <t>1d</t>
+  </si>
+  <si>
+    <t>1m</t>
+  </si>
+  <si>
+    <t>3m</t>
+  </si>
+  <si>
+    <t>6m</t>
+  </si>
+  <si>
+    <t>9m</t>
+  </si>
+  <si>
+    <t>1y</t>
+  </si>
+  <si>
+    <t>1.5y</t>
+  </si>
+  <si>
+    <t>2y</t>
+  </si>
+  <si>
+    <t>3y</t>
+  </si>
+  <si>
+    <t>4y</t>
+  </si>
+  <si>
+    <t>5y</t>
+  </si>
+  <si>
+    <t>6y</t>
+  </si>
+  <si>
+    <t>7y</t>
+  </si>
+  <si>
+    <t>8y</t>
+  </si>
+  <si>
+    <t>9y</t>
+  </si>
+  <si>
+    <t>10y</t>
+  </si>
+  <si>
+    <t>15y</t>
+  </si>
+  <si>
+    <t>20y</t>
+  </si>
+  <si>
+    <t>30y</t>
+  </si>
+  <si>
+    <t>Ближайшее значение</t>
+  </si>
+  <si>
+    <t>Значение MOEX</t>
+  </si>
+  <si>
+    <t>Интерполяция</t>
+  </si>
+  <si>
+    <t>Экстраполяция</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +140,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,179 +434,471 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>срок_в_годах</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ставка</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>0.0027</v>
+      </c>
+      <c r="C2">
         <v>0.0028</v>
       </c>
-      <c r="B2" t="n">
+      <c r="D2">
         <v>13.59</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.0833</v>
+      </c>
+      <c r="C3">
         <v>0.0417</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D3">
         <v>13.59</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>0.25</v>
+      </c>
+      <c r="C4">
         <v>0.1667</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D4">
         <v>13.59</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0.5</v>
+      </c>
+      <c r="C5">
         <v>0.375</v>
       </c>
-      <c r="B5" t="n">
-        <v>13.47</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="D5">
+        <v>13.35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0.75</v>
+      </c>
+      <c r="C6">
         <v>0.625</v>
       </c>
-      <c r="B6" t="n">
-        <v>13.385</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="D6">
+        <v>13.42</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
         <v>0.875</v>
       </c>
-      <c r="B7" t="n">
-        <v>13.525</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="D7">
+        <v>13.63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>1.5</v>
+      </c>
+      <c r="C8">
         <v>1.25</v>
       </c>
-      <c r="B8" t="n">
-        <v>13.8675</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="D8">
+        <v>14.105</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
         <v>1.75</v>
       </c>
-      <c r="B9" t="n">
-        <v>14.3425</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="D9">
+        <v>14.58</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
         <v>2.5</v>
       </c>
-      <c r="B10" t="n">
-        <v>14.82</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="D10">
+        <v>15.06</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
         <v>3.5</v>
       </c>
-      <c r="B11" t="n">
-        <v>15.15</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="D11">
+        <v>15.24</v>
+      </c>
+      <c r="E11" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
         <v>4.5</v>
       </c>
-      <c r="B12" t="n">
-        <v>15.33</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="D12">
+        <v>15.42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
         <v>5.5</v>
       </c>
-      <c r="B13" t="n">
-        <v>15.4575</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="D13">
+        <v>15.495</v>
+      </c>
+      <c r="E13" t="s">
+        <v>28</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>7</v>
+      </c>
+      <c r="C14">
         <v>6.5</v>
       </c>
-      <c r="B14" t="n">
-        <v>15.5325</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="D14">
+        <v>15.57</v>
+      </c>
+      <c r="E14" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
         <v>7.5</v>
       </c>
-      <c r="B15" t="n">
-        <v>15.59</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="D15">
+        <v>15.61</v>
+      </c>
+      <c r="E15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16">
+        <v>9</v>
+      </c>
+      <c r="C16">
         <v>8.5</v>
       </c>
-      <c r="B16" t="n">
-        <v>15.63</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="D16">
+        <v>15.65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
         <v>9.5</v>
       </c>
-      <c r="B17" t="n">
-        <v>15.67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="D17">
+        <v>15.69</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18">
         <v>12.5</v>
       </c>
-      <c r="B18" t="n">
-        <v>15.765</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="D18">
+        <v>15.84</v>
+      </c>
+      <c r="E18" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="C19">
         <v>17.5</v>
       </c>
-      <c r="B19" t="n">
-        <v>15.895</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="D19">
+        <v>15.95</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" t="n">
-        <v>16.025</v>
+      <c r="B20">
+        <v>30</v>
+      </c>
+      <c r="C20">
+        <v>25</v>
+      </c>
+      <c r="D20">
+        <v>16.17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>